--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/oct-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M244"/>
+  <dimension ref="A1:M268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4469-937-CM26</t>
+          <t>876-214-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>599.53</v>
+        <v>11839.38</v>
       </c>
     </row>
     <row r="4">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>876-214-CM26</t>
+          <t>4469-937-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -859,22 +859,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11839.38</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="8">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2859-1172-CM26</t>
+          <t>2859-1174-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2057-505-CM26</t>
+          <t>2859-1172-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1443.35</v>
+        <v>508.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3553-428-CM26</t>
+          <t>2057-505-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1812.29</v>
+        <v>1443.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1465-499-CM26</t>
+          <t>3553-428-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1639,22 +1639,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15146.15</v>
+        <v>1812.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2859-1174-CM26</t>
+          <t>1465-499-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1709,17 +1709,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>508.21</v>
+        <v>15146.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>707422-179-CM26</t>
+          <t>730566-281-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1769,37 +1769,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5684.81</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>730566-281-CM26</t>
+          <t>707422-179-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1834,37 +1834,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1701.5</v>
+        <v>5684.81</v>
       </c>
     </row>
     <row r="23">
@@ -2334,7 +2334,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057489-11238-CM26</t>
+          <t>4343-319-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1445.27</v>
+        <v>25385.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3950-1551-CM26</t>
+          <t>1057489-11238-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>13100.57</v>
+        <v>1445.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5911-192-CM26</t>
+          <t>3950-1551-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>482.32</v>
+        <v>13100.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1463-408-CM26</t>
+          <t>5911-192-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9179.85</v>
+        <v>482.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4343-319-CM26</t>
+          <t>1463-408-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>25385.35</v>
+        <v>9179.85</v>
       </c>
     </row>
     <row r="35">
@@ -2724,7 +2724,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1681-754-CM26</t>
+          <t>605-351-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2744,22 +2744,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.006.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>734.39</v>
+        <v>1370.81</v>
       </c>
     </row>
     <row r="37">
@@ -3114,7 +3114,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>605-351-CM26</t>
+          <t>1681-754-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3134,22 +3134,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.006.000-5</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Consejo de Defensa del Estado</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1370.81</v>
+        <v>734.39</v>
       </c>
     </row>
     <row r="43">
@@ -3439,7 +3439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1626-206-CM26</t>
+          <t>3506-752-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3459,22 +3459,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5694.54</v>
+        <v>2055.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3474-555-CM26</t>
+          <t>1626-206-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1103.1</v>
+        <v>5694.54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057531-446-CM26</t>
+          <t>3474-555-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,17 +3594,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13302.64</v>
+        <v>1103.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2310-794-CM26</t>
+          <t>1057531-446-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>57835.66</v>
+        <v>13302.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1051765-899-CM26</t>
+          <t>2310-794-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>255.82</v>
+        <v>57835.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3506-752-CM26</t>
+          <t>5588-26-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3784,22 +3784,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2055.2</v>
+        <v>7298.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5588-26-CM26</t>
+          <t>1511-1191-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7298.52</v>
+        <v>24079.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2115-758-CM26</t>
+          <t>1057370-576-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3914,22 +3914,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.061.030-k</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3847.53</v>
+        <v>13126.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1079969-196-CM26</t>
+          <t>1079969-200-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>315.89</v>
+        <v>840.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079969-197-CM26</t>
+          <t>1079969-199-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>327.92</v>
+        <v>514.4400000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1511-1191-CM26</t>
+          <t>1079969-198-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>24079.57</v>
+        <v>1083.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079969-199-CM26</t>
+          <t>1079969-197-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>514.4400000000001</v>
+        <v>327.92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079969-200-CM26</t>
+          <t>1079969-196-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>840.36</v>
+        <v>315.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057370-576-CM26</t>
+          <t>2115-758-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4304,22 +4304,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>65.061.030-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>13126.84</v>
+        <v>3847.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079969-198-CM26</t>
+          <t>1051765-899-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4369,32 +4369,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1083.04</v>
+        <v>255.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2066-466-CM26</t>
+          <t>542343-102-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.240-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hospital Galvarino</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>12151.6</v>
+        <v>24302.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1368-76-CM26</t>
+          <t>2202-1105-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1088.81</v>
+        <v>21771.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3474-560-CM26</t>
+          <t>2059-516-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4564,22 +4564,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.602.261-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>16512.13</v>
+        <v>14245.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057389-4424-CM26</t>
+          <t>2085-832-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>72192.52</v>
+        <v>2025.23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2059-516-CM26</t>
+          <t>3474-560-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.261-k</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO OCTAY</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14245.83</v>
+        <v>16512.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>542343-102-CM26</t>
+          <t>1368-76-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>24302.79</v>
+        <v>1088.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2202-1105-CM26</t>
+          <t>1057389-4424-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>21771.25</v>
+        <v>72192.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2085-832-CM26</t>
+          <t>2066-466-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.240-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>Hospital Galvarino</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2025.23</v>
+        <v>12151.6</v>
       </c>
     </row>
     <row r="70">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5064,7 +5064,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057540-2421-CM26</t>
+          <t>976780-11-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>75946.23</v>
+        <v>687.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1623-459-CM26</t>
+          <t>1057540-2421-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5154,17 +5154,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>12399.59</v>
+        <v>75946.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4778-694-CM26</t>
+          <t>1623-459-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>65841.33</v>
+        <v>12399.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2294-2178-CM26</t>
+          <t>4778-694-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5279,32 +5279,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>14319.57</v>
+        <v>65841.33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1626-189-CM26</t>
+          <t>2294-2178-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5344,32 +5344,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1860.54</v>
+        <v>14319.57</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>976780-11-CM26</t>
+          <t>1626-189-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>687.13</v>
+        <v>1860.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057384-806-CM26</t>
+          <t>1661-658-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,17 +5479,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>32233.32</v>
+        <v>16694.56</v>
       </c>
     </row>
     <row r="79">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1661-658-CM26</t>
+          <t>1057384-806-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>16694.56</v>
+        <v>32233.32</v>
       </c>
     </row>
     <row r="83">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5178-4470-CM26</t>
+          <t>1536-225-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,32 +6259,32 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>24194.95</v>
+        <v>967.8</v>
       </c>
     </row>
     <row r="91">
@@ -6624,7 +6624,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2146-553-CM26</t>
+          <t>5178-4470-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6644,32 +6644,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3358.54</v>
+        <v>24194.95</v>
       </c>
     </row>
     <row r="97">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1536-225-CM26</t>
+          <t>898-3407-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6774,37 +6774,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>967.8</v>
+        <v>21393.43</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>898-3407-CM26</t>
+          <t>2146-553-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,27 +6844,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>21393.43</v>
+        <v>3358.54</v>
       </c>
     </row>
     <row r="100">
@@ -6949,7 +6949,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1511-1205-CM26</t>
+          <t>1621-294-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>89.84999999999999</v>
+        <v>10996.57</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1511-1204-CM26</t>
+          <t>1867-300-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7039,17 +7039,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>44.93</v>
+        <v>2684.59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1556-274-CM26</t>
+          <t>1079969-204-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,17 +7104,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10220.51</v>
+        <v>1094.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1079969-205-CM26</t>
+          <t>995118-151-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2013.69</v>
+        <v>353.42</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079969-204-CM26</t>
+          <t>1556-274-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7234,17 +7234,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1094.2</v>
+        <v>10220.51</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1867-300-CM26</t>
+          <t>1511-1204-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,17 +7299,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2684.59</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1621-294-CM26</t>
+          <t>1511-1205-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>10996.57</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>995118-151-CM26</t>
+          <t>1079969-205-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>353.42</v>
+        <v>2013.69</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2147-519-CM26</t>
+          <t>4452-934-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7494,27 +7494,27 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4413.62</v>
+        <v>34329.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1558-372-CM26</t>
+          <t>707425-196-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7559,32 +7559,32 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12739.69</v>
+        <v>5102.85</v>
       </c>
     </row>
     <row r="111">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4452-934-CM26</t>
+          <t>2147-519-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,27 +7884,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>34329.69</v>
+        <v>4413.62</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>707425-196-CM26</t>
+          <t>1558-372-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7944,37 +7944,37 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5102.85</v>
+        <v>12739.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5013-67-CM26</t>
+          <t>1057500-467-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8009,17 +8009,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>65.455.650-4</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>605.86</v>
+        <v>38053.97</v>
       </c>
     </row>
     <row r="118">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057500-467-CM26</t>
+          <t>1075337-10069-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8399,22 +8399,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>38053.97</v>
+        <v>27354.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1075337-10069-CM26</t>
+          <t>5013-67-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>65.455.650-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>27354.4</v>
+        <v>605.86</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2048-2995-CM26</t>
+          <t>707416-97-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,17 +8534,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>13521.73</v>
+        <v>5227.79</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>707424-86-CM26</t>
+          <t>2137-909-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8594,32 +8594,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>916.5599999999999</v>
+        <v>12966.77</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>707424-88-CM26</t>
+          <t>2859-1288-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,32 +8659,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2138.65</v>
+        <v>489.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2137-909-CM26</t>
+          <t>3506-778-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8724,22 +8724,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>12966.77</v>
+        <v>19372.14</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3506-778-CM26</t>
+          <t>734-748-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>19372.14</v>
+        <v>37771.05</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2859-1288-CM26</t>
+          <t>707424-88-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,32 +8854,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>489.4</v>
+        <v>2138.65</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3945-731-CM26</t>
+          <t>707424-86-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,27 +8924,27 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>15462.83</v>
+        <v>916.5599999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>734-748-CM26</t>
+          <t>2048-2995-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8984,22 +8984,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>37771.05</v>
+        <v>13521.73</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1497-272-CM26</t>
+          <t>3945-731-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9054,27 +9054,27 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2317.86</v>
+        <v>15462.83</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>707416-97-CM26</t>
+          <t>1497-272-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5227.79</v>
+        <v>2317.86</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2046-496-CM26</t>
+          <t>1376-756-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9179,32 +9179,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>18911.75</v>
+        <v>326.27</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2324-1423-CM26</t>
+          <t>2046-496-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9244,37 +9244,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>35665.13</v>
+        <v>18911.75</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1978-1129-CM26</t>
+          <t>2324-1423-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9309,37 +9309,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6994.36</v>
+        <v>35665.13</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2140-921-CM26</t>
+          <t>1978-1129-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9374,22 +9374,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>125.9</v>
+        <v>6994.36</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2140-920-CM26</t>
+          <t>2140-921-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>10965.16</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3374-142-CM26</t>
+          <t>2140-920-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9509,17 +9509,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8156.69</v>
+        <v>10965.16</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057438-299-CM26</t>
+          <t>3374-142-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,27 +9574,27 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6731.87</v>
+        <v>8156.69</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4696-25-CM26</t>
+          <t>1057438-299-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9634,32 +9634,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>272.54</v>
+        <v>6731.87</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1057541-896-CM26</t>
+          <t>4696-25-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1763.88</v>
+        <v>272.54</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1376-756-CM26</t>
+          <t>1057541-896-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,27 +9769,27 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>326.27</v>
+        <v>1763.88</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3949-420-CM26</t>
+          <t>1079639-828-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>14378.36</v>
+        <v>5258.28</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>655348-87-CM26</t>
+          <t>3949-420-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>364.73</v>
+        <v>14378.36</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1692-728-CM26</t>
+          <t>655348-87-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>13082.16</v>
+        <v>364.73</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1079639-829-CM26</t>
+          <t>1692-728-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10029,17 +10029,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>39004.2</v>
+        <v>13082.16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1079639-830-CM26</t>
+          <t>1079639-829-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>24770.31</v>
+        <v>39004.2</v>
       </c>
     </row>
     <row r="150">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1665-10399-CM26</t>
+          <t>1079639-831-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>9388.65</v>
+        <v>17373.41</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1661-665-CM26</t>
+          <t>1665-10399-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>47.66</v>
+        <v>9388.65</v>
       </c>
     </row>
     <row r="153">
@@ -10394,7 +10394,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1079445-681-CM26</t>
+          <t>2139-866-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10414,32 +10414,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2277.66</v>
+        <v>7535.94</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1079639-828-CM26</t>
+          <t>1079639-830-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5258.28</v>
+        <v>24770.31</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1079639-831-CM26</t>
+          <t>2151-404-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10544,22 +10544,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>17373.41</v>
+        <v>8542.719999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2139-866-CM26</t>
+          <t>1079445-681-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10609,32 +10609,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7535.94</v>
+        <v>2277.66</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3439-151-CM26</t>
+          <t>1222283-40-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.112.000-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ACADEMIA NACIONAL DE ESTUDIOS POLITICOS Y ESTRATEGICOS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1445.63</v>
+        <v>1610.89</v>
       </c>
     </row>
     <row r="159">
@@ -10784,7 +10784,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2151-404-CM26</t>
+          <t>2294-1918-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,27 +10809,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>8542.719999999999</v>
+        <v>44339.11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2294-1918-CM26</t>
+          <t>3970-64-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10874,27 +10874,27 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>44339.11</v>
+        <v>17498.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3970-64-CM26</t>
+          <t>1867-303-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10934,17 +10934,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>17498.48</v>
+        <v>2419.05</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1867-303-CM26</t>
+          <t>1274667-397-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,22 +10999,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2419.05</v>
+        <v>13707.79</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2085-842-CM26</t>
+          <t>1661-665-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11069,17 +11069,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1985.75</v>
+        <v>47.66</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1274667-397-CM26</t>
+          <t>3439-151-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11129,22 +11129,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>13707.79</v>
+        <v>1445.63</v>
       </c>
     </row>
     <row r="166">
@@ -11434,7 +11434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1222283-40-CM26</t>
+          <t>2085-842-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,27 +11459,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.112.000-1</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ACADEMIA NACIONAL DE ESTUDIOS POLITICOS Y ESTRATEGICOS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1610.89</v>
+        <v>1985.75</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1057476-995-CM26</t>
+          <t>1499-5589-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11519,17 +11519,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.608.003-2</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2131.19</v>
+        <v>1429.89</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1079694-357-CM26</t>
+          <t>2294-2287-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,27 +11589,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2039.49</v>
+        <v>32609.74</v>
       </c>
     </row>
     <row r="173">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2294-2287-CM26</t>
+          <t>1057476-995-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11714,32 +11714,32 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.608.003-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>32609.74</v>
+        <v>2131.19</v>
       </c>
     </row>
     <row r="175">
@@ -11824,7 +11824,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1079689-447-CM26</t>
+          <t>1079505-671-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>135.44</v>
+        <v>1880.15</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1079505-671-CM26</t>
+          <t>3950-1613-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11909,22 +11909,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1880.15</v>
+        <v>5321.79</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3950-1613-CM26</t>
+          <t>1079659-418-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11974,22 +11974,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5321.79</v>
+        <v>4564.95</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1079659-418-CM26</t>
+          <t>896-38-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12044,17 +12044,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4564.95</v>
+        <v>4425.41</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>896-38-CM26</t>
+          <t>1079689-447-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,17 +12109,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4425.41</v>
+        <v>135.44</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1499-5589-CM26</t>
+          <t>1079694-357-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.608.402-k</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DEL TORAX</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1429.89</v>
+        <v>2039.49</v>
       </c>
     </row>
     <row r="182">
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1078177-957-CM26</t>
+          <t>1078177-961-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>17481.04</v>
+        <v>30085.44</v>
       </c>
     </row>
     <row r="185">
@@ -12474,7 +12474,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1079580-410-CM26</t>
+          <t>1078177-958-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>41035.74</v>
+        <v>6849.41</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>691-21-CM26</t>
+          <t>1078177-957-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12564,27 +12564,27 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.802.007-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1148.27</v>
+        <v>17481.04</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1606-355-CM26</t>
+          <t>418-3432-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>946.05</v>
+        <v>36186.48</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1079505-662-CM26</t>
+          <t>617807-5571-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,17 +12694,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1409.12</v>
+        <v>49070.21</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3544-246-CM26</t>
+          <t>617807-5570-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,13 +12793,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1016.17</v>
+        <v>17119.75</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5684-586-CM26</t>
+          <t>3544-246-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12824,17 +12824,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3445.99</v>
+        <v>1016.17</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>617807-5571-CM26</t>
+          <t>1079505-662-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,17 +12889,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>49070.21</v>
+        <v>1409.12</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4955-164-CM26</t>
+          <t>5684-586-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>579.22</v>
+        <v>3445.99</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>418-3432-CM26</t>
+          <t>1606-355-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,17 +13019,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>36186.48</v>
+        <v>946.05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1078177-958-CM26</t>
+          <t>691-21-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13084,27 +13084,27 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.802.007-K</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6849.41</v>
+        <v>1148.27</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1078177-961-CM26</t>
+          <t>1079580-410-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>30085.44</v>
+        <v>41035.74</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>617807-5570-CM26</t>
+          <t>4955-164-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,17 +13214,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>17119.75</v>
+        <v>579.22</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1079516-1101-CM26</t>
+          <t>4100-174-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,12 +13274,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -13289,17 +13289,17 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>14953.82</v>
+        <v>175.7</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1643-2175-CM26</t>
+          <t>3283-60-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13339,32 +13339,32 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>42049.2</v>
+        <v>9346.51</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3553-458-CM26</t>
+          <t>1079969-206-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,13 +13443,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1003.41</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>764-252-CM26</t>
+          <t>3553-458-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13474,17 +13474,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1902.77</v>
+        <v>1003.41</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3283-60-CM26</t>
+          <t>1643-2175-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13534,32 +13534,32 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13573,13 +13573,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>9346.51</v>
+        <v>42049.2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4100-174-CM26</t>
+          <t>1079516-1101-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13599,12 +13599,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -13614,17 +13614,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>175.7</v>
+        <v>14953.82</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1079516-1100-CM26</t>
+          <t>764-252-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,32 +13664,32 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>13073.99</v>
+        <v>1902.77</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1079969-206-CM26</t>
+          <t>1079516-1100-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,12 +13729,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -13744,17 +13744,17 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>7.99</v>
+        <v>13073.99</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1079596-201-CM26</t>
+          <t>1087-241-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13814,12 +13814,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>145.16</v>
+        <v>3514.49</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1079969-208-CM26</t>
+          <t>1079596-201-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -13874,17 +13874,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>7.99</v>
+        <v>145.16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079969-207-CM26</t>
+          <t>1079969-208-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13969,7 +13969,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2362-99-CM26</t>
+          <t>1079969-207-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13989,22 +13989,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1809.22</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1087-241-CM26</t>
+          <t>2362-99-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,27 +14059,27 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3514.49</v>
+        <v>1809.22</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1079516-1099-CM26</t>
+          <t>1043030-78-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14119,32 +14119,32 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14158,13 +14158,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>38257.59</v>
+        <v>715.12</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2445-2554-CM26</t>
+          <t>1079516-1099-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14179,37 +14179,37 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>52096.12</v>
+        <v>38257.59</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1057431-3253-CM26</t>
+          <t>2445-2554-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,27 +14254,27 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.602.295-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8790.9</v>
+        <v>52096.12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1523-2425-CM26</t>
+          <t>1057431-3253-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14319,27 +14319,27 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.602.295-4</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>610.5</v>
+        <v>8790.9</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3438-217-CM26</t>
+          <t>1523-2425-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,22 +14379,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.101.022-2</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>426.25</v>
+        <v>610.5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2294-2243-CM26</t>
+          <t>1172239-126-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14449,27 +14449,27 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>407.39</v>
+        <v>2291.57</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2294-2242-CM26</t>
+          <t>1172239-124-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14514,27 +14514,27 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>12166.88</v>
+        <v>2291.57</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2294-2219-CM26</t>
+          <t>3438-217-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,32 +14574,32 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.101.022-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4784.13</v>
+        <v>426.25</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2199-488-CM26</t>
+          <t>2199-489-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1656.48</v>
+        <v>1770.21</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1294154-14-CM26</t>
+          <t>2199-488-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.608.403-8</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5579.63</v>
+        <v>1656.48</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2078-1173-CM26</t>
+          <t>2294-2243-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14774,27 +14774,27 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>28244.57</v>
+        <v>407.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2408-1070-CM26</t>
+          <t>2294-2242-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -14839,27 +14839,27 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>27921.64</v>
+        <v>12166.88</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2205-194-CM26</t>
+          <t>2294-2219-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14904,27 +14904,27 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>6912.16</v>
+        <v>4784.13</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5911-204-CM26</t>
+          <t>2078-1173-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14969,17 +14969,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>6058.51</v>
+        <v>28244.57</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1028871-654-CM26</t>
+          <t>2408-1070-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2416.09</v>
+        <v>27921.64</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1057388-598-CM26</t>
+          <t>2205-194-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15094,22 +15094,22 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>11769.29</v>
+        <v>6912.16</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3047-618-CM26</t>
+          <t>5911-204-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15159,22 +15159,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>510.75</v>
+        <v>6058.51</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>707429-124-CM26</t>
+          <t>1294154-14-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5409.27</v>
+        <v>5579.63</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4406-873-CM26</t>
+          <t>1028871-654-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,17 +15294,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>10096.47</v>
+        <v>2416.09</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3172-291-CM26</t>
+          <t>1057388-598-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2562.95</v>
+        <v>11769.29</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1079639-847-CM26</t>
+          <t>3047-618-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15424,17 +15424,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>358.49</v>
+        <v>510.75</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3481-139-CM26</t>
+          <t>707429-124-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15489,27 +15489,27 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>5109.55</v>
+        <v>5409.27</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2294-2240-CM26</t>
+          <t>4406-873-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15554,27 +15554,27 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>153.29</v>
+        <v>10096.47</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3481-137-CM26</t>
+          <t>3172-291-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15619,27 +15619,27 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>715.34</v>
+        <v>2562.95</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2047-92-CM26</t>
+          <t>1079639-847-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,22 +15679,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>60.511.073-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LINARES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>902.4400000000001</v>
+        <v>358.49</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>759-445-CM26</t>
+          <t>3481-139-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -15749,27 +15749,27 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>27752.5</v>
+        <v>5109.55</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3515-479-CM26</t>
+          <t>2294-2240-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -15814,27 +15814,27 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>6961.36</v>
+        <v>153.29</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3544-254-CM26</t>
+          <t>3481-137-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -15889,17 +15889,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2027.2</v>
+        <v>715.34</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1383-320-CM26</t>
+          <t>2047-92-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>60.511.073-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LINARES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>8794.950000000001</v>
+        <v>902.4400000000001</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1099834-111-CM26</t>
+          <t>4301-712-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3040.81</v>
+        <v>27589.53</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>951405-357-CM26</t>
+          <t>1057489-11837-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -16074,17 +16074,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3770.6</v>
+        <v>1649.91</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1557-378-CM26</t>
+          <t>759-445-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -16139,17 +16139,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>18133.37</v>
+        <v>27752.5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1622-1347-CM26</t>
+          <t>3515-479-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -16204,17 +16204,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -16238,72 +16238,1632 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>24326.46</v>
+        <v>6961.36</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t>1604-162-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>60.511.020-7</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>668.98</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1604-161-CM26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>60.511.020-7</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>547.35</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1070329-340-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>61.980.370-1</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>CESFAM LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>13684.75</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1079659-425-CM26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>52104.24</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
           <t>4406-887-CM26</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2239-1-LR26</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>69.180.800-9</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M244" s="2" t="n">
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="n">
         <v>13095.65</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1705-699-CM26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>61.606.603-k</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>23312.86</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1622-1347-CM26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>61.602.141-9</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>24326.46</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>3544-254-CM26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>61.101.062-1</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>2027.2</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>951405-357-CM26</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>3770.6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1099834-111-CM26</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>62.000.640-8</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>3040.81</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1383-320-CM26</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>61.602.242-3</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>HOSPITAL VILCUN</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="n">
+        <v>8794.950000000001</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1079454-478-CM26</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="n">
+        <v>1327.09</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>3436-731-CM26</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>61.101.027-3</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>1495.31</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2410-504-CM26</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>24839.65</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1557-378-CM26</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>18133.37</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1057514-353-CM26</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>61.607.006-1</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>14210.42</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1099402-559-CM26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>62.000.620-3</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>13853.69</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1057390-825-CM26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>61.955.100-1</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>38592.42</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1057506-4811-CM26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>61.602.194-K</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>16156.17</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1371-69-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>75.971.200-5</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Comité de Seguros del Agro</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>492.99</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>652-380-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.954.500-1</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>42246.82</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1079689-450-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>23669.03</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1202512-44-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>60.511.090-8</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>403.9</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1057533-498-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>61.980.080-K</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>HOSPITAL DEL PERPETUO SOCORRO DE QUILACAHUIN</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>403.74</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>3950-1682-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>12207.57</v>
       </c>
     </row>
   </sheetData>
